--- a/tasks/finalpool/terminal-canvas-gform-gcal-excel-email/groundtruth_workspace/Quiz_Performance_Report.xlsx
+++ b/tasks/finalpool/terminal-canvas-gform-gcal-excel-email/groundtruth_workspace/Quiz_Performance_Report.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SCALE</t>
+          <t>MULTIPLE_CHOICE</t>
         </is>
       </c>
     </row>
